--- a/templates/quotation_template.xlsx
+++ b/templates/quotation_template.xlsx
@@ -3,20 +3,15 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\steven.lee\AppData\Local\Temp\claude\C--Users-steven-lee\8a32833b-4f13-4438-9fb0-49c896322216\scratchpad\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2827265B-492F-494A-AAF7-51048C8BB94F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CEE9E6BF-E655-4F44-B520-D7C18CE8D9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="14400" windowHeight="8170" tabRatio="1000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="報價單 " sheetId="83" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'報價單 '!$A$1:$K$95</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'報價單 '!$A$1:$K$103</definedName>
   </definedNames>
   <calcPr calcId="191029" concurrentManualCount="8"/>
   <extLst>
@@ -243,19 +238,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="10">
+  <numFmts count="9">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="176" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-;\-&quot;\&quot;* #,##0.00_-;_-&quot;\&quot;* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="&quot;NT$&quot;#,##0"/>
-    <numFmt numFmtId="181" formatCode="_-&quot;\&quot;* #,##0_-;\-&quot;\&quot;* #,##0_-;_-&quot;\&quot;* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="186" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="187" formatCode="#,##0_ "/>
-    <numFmt numFmtId="188" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="189" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-;\-&quot;\&quot;* #,##0.00_-;_-&quot;\&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="&quot;NT$&quot;#,##0"/>
+    <numFmt numFmtId="180" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="181" formatCode="#,##0_ "/>
+    <numFmt numFmtId="182" formatCode="_(&quot;$&quot;* #,##0_);_(&quot;$&quot;* \(#,##0\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+    <numFmt numFmtId="183" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="32">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -465,6 +459,13 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微軟正黑體"/>
+      <family val="2"/>
+      <charset val="136"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -597,7 +598,7 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="178" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="177" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
@@ -643,7 +644,7 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="102">
+  <cellXfs count="103">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="11" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
@@ -699,7 +700,7 @@
     <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="189" fontId="16" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="16" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="15" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -714,7 +715,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="186" fontId="14" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="14" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
@@ -746,10 +747,10 @@
     <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="187" fontId="19" fillId="0" borderId="6" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="19" fillId="0" borderId="0" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="19" fillId="0" borderId="6" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="19" fillId="0" borderId="0" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="4" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -783,7 +784,7 @@
     <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="176" fontId="24" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="187" fontId="25" fillId="0" borderId="6" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="181" fontId="25" fillId="0" borderId="6" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="6" xfId="15" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -804,7 +805,7 @@
     <xf numFmtId="49" fontId="14" fillId="4" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="6" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="26" fillId="0" borderId="6" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="14" fillId="0" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -813,19 +814,19 @@
     <xf numFmtId="176" fontId="14" fillId="5" borderId="0" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="26" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="26" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="26" fillId="0" borderId="0" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="26" fillId="0" borderId="0" xfId="12" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="22" fontId="14" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="19" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="19" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="13" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -843,13 +844,22 @@
     <xf numFmtId="49" fontId="14" fillId="4" borderId="2" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="186" fontId="25" fillId="0" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="30" fillId="4" borderId="6" xfId="14" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="11" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -865,7 +875,7 @@
     <xf numFmtId="176" fontId="19" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="188" fontId="19" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="182" fontId="19" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="13" applyFont="1" applyAlignment="1">
@@ -883,38 +893,32 @@
     <xf numFmtId="0" fontId="14" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="19" fillId="0" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="19" fillId="0" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="19" fillId="0" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="19" fillId="0" borderId="5" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="19" fillId="0" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="19" fillId="0" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="25" fillId="0" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="2" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="186" fontId="25" fillId="0" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="180" fontId="25" fillId="0" borderId="7" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="189" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="183" fontId="18" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="2" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="5" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="7" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="37" fontId="14" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="37" fontId="31" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="28">
@@ -1951,7 +1955,7 @@
     <tabColor rgb="FFFF0000"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:O95"/>
+  <dimension ref="A2:O103"/>
   <sheetFormatPr defaultColWidth="10.453125" defaultRowHeight="15.5"/>
   <cols>
     <col min="1" max="1" width="3.1796875" style="1" customWidth="1"/>
@@ -2114,8 +2118,8 @@
       <c r="O14" s="79"/>
     </row>
     <row r="15" spans="2:15">
-      <c r="B15" s="80"/>
-      <c r="C15" s="80"/>
+      <c r="B15" s="83"/>
+      <c r="C15" s="83"/>
       <c r="J15" s="7" t="s">
         <v>14</v>
       </c>
@@ -2124,11 +2128,11 @@
       <c r="B16" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="81" t="s">
+      <c r="C16" s="84" t="s">
         <v>4</v>
       </c>
-      <c r="D16" s="82"/>
-      <c r="E16" s="83"/>
+      <c r="D16" s="85"/>
+      <c r="E16" s="86"/>
       <c r="F16" s="13" t="s">
         <v>12</v>
       </c>
@@ -2151,9 +2155,9 @@
     </row>
     <row r="17" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B17" s="78"/>
-      <c r="C17" s="98"/>
-      <c r="D17" s="99"/>
-      <c r="E17" s="100"/>
+      <c r="C17" s="80"/>
+      <c r="D17" s="81"/>
+      <c r="E17" s="82"/>
       <c r="F17" s="58"/>
       <c r="G17" s="39"/>
       <c r="H17" s="59"/>
@@ -2166,9 +2170,9 @@
     </row>
     <row r="18" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B18" s="78"/>
-      <c r="C18" s="98"/>
-      <c r="D18" s="99"/>
-      <c r="E18" s="100"/>
+      <c r="C18" s="80"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="82"/>
       <c r="F18" s="58"/>
       <c r="G18" s="39"/>
       <c r="H18" s="59"/>
@@ -2181,9 +2185,9 @@
     </row>
     <row r="19" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B19" s="78"/>
-      <c r="C19" s="98"/>
-      <c r="D19" s="99"/>
-      <c r="E19" s="100"/>
+      <c r="C19" s="80"/>
+      <c r="D19" s="81"/>
+      <c r="E19" s="82"/>
       <c r="F19" s="58"/>
       <c r="G19" s="39"/>
       <c r="H19" s="59"/>
@@ -2196,9 +2200,9 @@
     </row>
     <row r="20" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B20" s="78"/>
-      <c r="C20" s="98"/>
-      <c r="D20" s="99"/>
-      <c r="E20" s="100"/>
+      <c r="C20" s="80"/>
+      <c r="D20" s="81"/>
+      <c r="E20" s="82"/>
       <c r="F20" s="58"/>
       <c r="G20" s="39"/>
       <c r="H20" s="59"/>
@@ -2211,9 +2215,9 @@
     </row>
     <row r="21" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B21" s="78"/>
-      <c r="C21" s="98"/>
-      <c r="D21" s="99"/>
-      <c r="E21" s="100"/>
+      <c r="C21" s="80"/>
+      <c r="D21" s="81"/>
+      <c r="E21" s="82"/>
       <c r="F21" s="58"/>
       <c r="G21" s="39"/>
       <c r="H21" s="59"/>
@@ -2226,9 +2230,9 @@
     </row>
     <row r="22" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B22" s="78"/>
-      <c r="C22" s="98"/>
-      <c r="D22" s="99"/>
-      <c r="E22" s="100"/>
+      <c r="C22" s="80"/>
+      <c r="D22" s="81"/>
+      <c r="E22" s="82"/>
       <c r="F22" s="58"/>
       <c r="G22" s="39"/>
       <c r="H22" s="59"/>
@@ -2241,9 +2245,9 @@
     </row>
     <row r="23" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B23" s="78"/>
-      <c r="C23" s="98"/>
-      <c r="D23" s="99"/>
-      <c r="E23" s="100"/>
+      <c r="C23" s="80"/>
+      <c r="D23" s="81"/>
+      <c r="E23" s="82"/>
       <c r="F23" s="58"/>
       <c r="G23" s="39"/>
       <c r="H23" s="59"/>
@@ -2256,9 +2260,9 @@
     </row>
     <row r="24" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B24" s="78"/>
-      <c r="C24" s="98"/>
-      <c r="D24" s="99"/>
-      <c r="E24" s="100"/>
+      <c r="C24" s="80"/>
+      <c r="D24" s="81"/>
+      <c r="E24" s="82"/>
       <c r="F24" s="58"/>
       <c r="G24" s="39"/>
       <c r="H24" s="59"/>
@@ -2271,9 +2275,9 @@
     </row>
     <row r="25" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B25" s="78"/>
-      <c r="C25" s="98"/>
-      <c r="D25" s="99"/>
-      <c r="E25" s="100"/>
+      <c r="C25" s="80"/>
+      <c r="D25" s="81"/>
+      <c r="E25" s="82"/>
       <c r="F25" s="58"/>
       <c r="G25" s="39"/>
       <c r="H25" s="59"/>
@@ -2286,9 +2290,9 @@
     </row>
     <row r="26" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B26" s="78"/>
-      <c r="C26" s="98"/>
-      <c r="D26" s="99"/>
-      <c r="E26" s="100"/>
+      <c r="C26" s="80"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="82"/>
       <c r="F26" s="58"/>
       <c r="G26" s="39"/>
       <c r="H26" s="59"/>
@@ -2301,9 +2305,9 @@
     </row>
     <row r="27" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B27" s="78"/>
-      <c r="C27" s="98"/>
-      <c r="D27" s="99"/>
-      <c r="E27" s="100"/>
+      <c r="C27" s="80"/>
+      <c r="D27" s="81"/>
+      <c r="E27" s="82"/>
       <c r="F27" s="58"/>
       <c r="G27" s="39"/>
       <c r="H27" s="59"/>
@@ -2316,9 +2320,9 @@
     </row>
     <row r="28" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B28" s="78"/>
-      <c r="C28" s="98"/>
-      <c r="D28" s="99"/>
-      <c r="E28" s="100"/>
+      <c r="C28" s="80"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="82"/>
       <c r="F28" s="58"/>
       <c r="G28" s="39"/>
       <c r="H28" s="59"/>
@@ -2331,9 +2335,9 @@
     </row>
     <row r="29" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B29" s="78"/>
-      <c r="C29" s="98"/>
-      <c r="D29" s="99"/>
-      <c r="E29" s="100"/>
+      <c r="C29" s="80"/>
+      <c r="D29" s="81"/>
+      <c r="E29" s="82"/>
       <c r="F29" s="58"/>
       <c r="G29" s="39"/>
       <c r="H29" s="59"/>
@@ -2346,9 +2350,9 @@
     </row>
     <row r="30" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B30" s="78"/>
-      <c r="C30" s="98"/>
-      <c r="D30" s="99"/>
-      <c r="E30" s="100"/>
+      <c r="C30" s="80"/>
+      <c r="D30" s="81"/>
+      <c r="E30" s="82"/>
       <c r="F30" s="58"/>
       <c r="G30" s="39"/>
       <c r="H30" s="59"/>
@@ -2361,9 +2365,9 @@
     </row>
     <row r="31" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B31" s="78"/>
-      <c r="C31" s="98"/>
-      <c r="D31" s="99"/>
-      <c r="E31" s="100"/>
+      <c r="C31" s="80"/>
+      <c r="D31" s="81"/>
+      <c r="E31" s="82"/>
       <c r="F31" s="58"/>
       <c r="G31" s="39"/>
       <c r="H31" s="59"/>
@@ -2376,9 +2380,9 @@
     </row>
     <row r="32" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B32" s="78"/>
-      <c r="C32" s="98"/>
-      <c r="D32" s="99"/>
-      <c r="E32" s="100"/>
+      <c r="C32" s="80"/>
+      <c r="D32" s="81"/>
+      <c r="E32" s="82"/>
       <c r="F32" s="58"/>
       <c r="G32" s="39"/>
       <c r="H32" s="59"/>
@@ -2391,9 +2395,9 @@
     </row>
     <row r="33" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B33" s="78"/>
-      <c r="C33" s="98"/>
-      <c r="D33" s="99"/>
-      <c r="E33" s="100"/>
+      <c r="C33" s="80"/>
+      <c r="D33" s="81"/>
+      <c r="E33" s="82"/>
       <c r="F33" s="58"/>
       <c r="G33" s="39"/>
       <c r="H33" s="59"/>
@@ -2406,9 +2410,9 @@
     </row>
     <row r="34" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B34" s="78"/>
-      <c r="C34" s="98"/>
-      <c r="D34" s="99"/>
-      <c r="E34" s="100"/>
+      <c r="C34" s="80"/>
+      <c r="D34" s="81"/>
+      <c r="E34" s="82"/>
       <c r="F34" s="58"/>
       <c r="G34" s="39"/>
       <c r="H34" s="59"/>
@@ -2421,9 +2425,9 @@
     </row>
     <row r="35" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B35" s="78"/>
-      <c r="C35" s="98"/>
-      <c r="D35" s="99"/>
-      <c r="E35" s="100"/>
+      <c r="C35" s="80"/>
+      <c r="D35" s="81"/>
+      <c r="E35" s="82"/>
       <c r="F35" s="58"/>
       <c r="G35" s="39"/>
       <c r="H35" s="59"/>
@@ -2436,9 +2440,9 @@
     </row>
     <row r="36" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B36" s="78"/>
-      <c r="C36" s="98"/>
-      <c r="D36" s="99"/>
-      <c r="E36" s="100"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="81"/>
+      <c r="E36" s="82"/>
       <c r="F36" s="58"/>
       <c r="G36" s="39"/>
       <c r="H36" s="59"/>
@@ -2451,9 +2455,9 @@
     </row>
     <row r="37" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B37" s="78"/>
-      <c r="C37" s="98"/>
-      <c r="D37" s="99"/>
-      <c r="E37" s="100"/>
+      <c r="C37" s="80"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
       <c r="F37" s="58"/>
       <c r="G37" s="39"/>
       <c r="H37" s="59"/>
@@ -2466,9 +2470,9 @@
     </row>
     <row r="38" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B38" s="78"/>
-      <c r="C38" s="98"/>
-      <c r="D38" s="99"/>
-      <c r="E38" s="100"/>
+      <c r="C38" s="80"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="82"/>
       <c r="F38" s="58"/>
       <c r="G38" s="39"/>
       <c r="H38" s="59"/>
@@ -2481,9 +2485,9 @@
     </row>
     <row r="39" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B39" s="78"/>
-      <c r="C39" s="98"/>
-      <c r="D39" s="99"/>
-      <c r="E39" s="100"/>
+      <c r="C39" s="80"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="82"/>
       <c r="F39" s="58"/>
       <c r="G39" s="39"/>
       <c r="H39" s="59"/>
@@ -2496,9 +2500,9 @@
     </row>
     <row r="40" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B40" s="78"/>
-      <c r="C40" s="98"/>
-      <c r="D40" s="99"/>
-      <c r="E40" s="100"/>
+      <c r="C40" s="80"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="82"/>
       <c r="F40" s="58"/>
       <c r="G40" s="39"/>
       <c r="H40" s="59"/>
@@ -2511,9 +2515,9 @@
     </row>
     <row r="41" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B41" s="78"/>
-      <c r="C41" s="98"/>
-      <c r="D41" s="99"/>
-      <c r="E41" s="100"/>
+      <c r="C41" s="80"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="82"/>
       <c r="F41" s="58"/>
       <c r="G41" s="39"/>
       <c r="H41" s="59"/>
@@ -2526,9 +2530,9 @@
     </row>
     <row r="42" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B42" s="78"/>
-      <c r="C42" s="98"/>
-      <c r="D42" s="99"/>
-      <c r="E42" s="100"/>
+      <c r="C42" s="80"/>
+      <c r="D42" s="81"/>
+      <c r="E42" s="82"/>
       <c r="F42" s="58"/>
       <c r="G42" s="39"/>
       <c r="H42" s="59"/>
@@ -2541,9 +2545,9 @@
     </row>
     <row r="43" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B43" s="78"/>
-      <c r="C43" s="98"/>
-      <c r="D43" s="99"/>
-      <c r="E43" s="100"/>
+      <c r="C43" s="80"/>
+      <c r="D43" s="81"/>
+      <c r="E43" s="82"/>
       <c r="F43" s="58"/>
       <c r="G43" s="39"/>
       <c r="H43" s="59"/>
@@ -2556,9 +2560,9 @@
     </row>
     <row r="44" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B44" s="78"/>
-      <c r="C44" s="98"/>
-      <c r="D44" s="99"/>
-      <c r="E44" s="100"/>
+      <c r="C44" s="80"/>
+      <c r="D44" s="81"/>
+      <c r="E44" s="82"/>
       <c r="F44" s="58"/>
       <c r="G44" s="39"/>
       <c r="H44" s="59"/>
@@ -2571,9 +2575,9 @@
     </row>
     <row r="45" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B45" s="78"/>
-      <c r="C45" s="98"/>
-      <c r="D45" s="99"/>
-      <c r="E45" s="100"/>
+      <c r="C45" s="80"/>
+      <c r="D45" s="81"/>
+      <c r="E45" s="82"/>
       <c r="F45" s="58"/>
       <c r="G45" s="39"/>
       <c r="H45" s="59"/>
@@ -2586,9 +2590,9 @@
     </row>
     <row r="46" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B46" s="78"/>
-      <c r="C46" s="98"/>
-      <c r="D46" s="99"/>
-      <c r="E46" s="100"/>
+      <c r="C46" s="80"/>
+      <c r="D46" s="81"/>
+      <c r="E46" s="82"/>
       <c r="F46" s="58"/>
       <c r="G46" s="39"/>
       <c r="H46" s="59"/>
@@ -2601,9 +2605,9 @@
     </row>
     <row r="47" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B47" s="78"/>
-      <c r="C47" s="98"/>
-      <c r="D47" s="99"/>
-      <c r="E47" s="100"/>
+      <c r="C47" s="80"/>
+      <c r="D47" s="81"/>
+      <c r="E47" s="82"/>
       <c r="F47" s="58"/>
       <c r="G47" s="39"/>
       <c r="H47" s="59"/>
@@ -2616,9 +2620,9 @@
     </row>
     <row r="48" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B48" s="78"/>
-      <c r="C48" s="98"/>
-      <c r="D48" s="99"/>
-      <c r="E48" s="100"/>
+      <c r="C48" s="80"/>
+      <c r="D48" s="81"/>
+      <c r="E48" s="82"/>
       <c r="F48" s="58"/>
       <c r="G48" s="39"/>
       <c r="H48" s="59"/>
@@ -2631,9 +2635,9 @@
     </row>
     <row r="49" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B49" s="78"/>
-      <c r="C49" s="98"/>
-      <c r="D49" s="99"/>
-      <c r="E49" s="100"/>
+      <c r="C49" s="80"/>
+      <c r="D49" s="81"/>
+      <c r="E49" s="82"/>
       <c r="F49" s="58"/>
       <c r="G49" s="39"/>
       <c r="H49" s="59"/>
@@ -2646,9 +2650,9 @@
     </row>
     <row r="50" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B50" s="78"/>
-      <c r="C50" s="98"/>
-      <c r="D50" s="99"/>
-      <c r="E50" s="100"/>
+      <c r="C50" s="80"/>
+      <c r="D50" s="81"/>
+      <c r="E50" s="82"/>
       <c r="F50" s="58"/>
       <c r="G50" s="39"/>
       <c r="H50" s="59"/>
@@ -2661,9 +2665,9 @@
     </row>
     <row r="51" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B51" s="78"/>
-      <c r="C51" s="98"/>
-      <c r="D51" s="99"/>
-      <c r="E51" s="100"/>
+      <c r="C51" s="80"/>
+      <c r="D51" s="81"/>
+      <c r="E51" s="82"/>
       <c r="F51" s="58"/>
       <c r="G51" s="39"/>
       <c r="H51" s="59"/>
@@ -2676,9 +2680,9 @@
     </row>
     <row r="52" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B52" s="78"/>
-      <c r="C52" s="98"/>
-      <c r="D52" s="99"/>
-      <c r="E52" s="100"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="81"/>
+      <c r="E52" s="82"/>
       <c r="F52" s="58"/>
       <c r="G52" s="39"/>
       <c r="H52" s="59"/>
@@ -2691,9 +2695,9 @@
     </row>
     <row r="53" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B53" s="78"/>
-      <c r="C53" s="98"/>
-      <c r="D53" s="99"/>
-      <c r="E53" s="100"/>
+      <c r="C53" s="80"/>
+      <c r="D53" s="81"/>
+      <c r="E53" s="82"/>
       <c r="F53" s="58"/>
       <c r="G53" s="39"/>
       <c r="H53" s="59"/>
@@ -2706,9 +2710,9 @@
     </row>
     <row r="54" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B54" s="78"/>
-      <c r="C54" s="98"/>
-      <c r="D54" s="99"/>
-      <c r="E54" s="100"/>
+      <c r="C54" s="80"/>
+      <c r="D54" s="81"/>
+      <c r="E54" s="82"/>
       <c r="F54" s="58"/>
       <c r="G54" s="39"/>
       <c r="H54" s="59"/>
@@ -2721,9 +2725,9 @@
     </row>
     <row r="55" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B55" s="78"/>
-      <c r="C55" s="98"/>
-      <c r="D55" s="99"/>
-      <c r="E55" s="100"/>
+      <c r="C55" s="80"/>
+      <c r="D55" s="81"/>
+      <c r="E55" s="82"/>
       <c r="F55" s="58"/>
       <c r="G55" s="39"/>
       <c r="H55" s="59"/>
@@ -2736,9 +2740,9 @@
     </row>
     <row r="56" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B56" s="78"/>
-      <c r="C56" s="98"/>
-      <c r="D56" s="99"/>
-      <c r="E56" s="100"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="81"/>
+      <c r="E56" s="82"/>
       <c r="F56" s="58"/>
       <c r="G56" s="39"/>
       <c r="H56" s="59"/>
@@ -2751,9 +2755,9 @@
     </row>
     <row r="57" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B57" s="78"/>
-      <c r="C57" s="98"/>
-      <c r="D57" s="99"/>
-      <c r="E57" s="100"/>
+      <c r="C57" s="80"/>
+      <c r="D57" s="81"/>
+      <c r="E57" s="82"/>
       <c r="F57" s="58"/>
       <c r="G57" s="39"/>
       <c r="H57" s="59"/>
@@ -2766,9 +2770,9 @@
     </row>
     <row r="58" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B58" s="78"/>
-      <c r="C58" s="98"/>
-      <c r="D58" s="99"/>
-      <c r="E58" s="100"/>
+      <c r="C58" s="80"/>
+      <c r="D58" s="81"/>
+      <c r="E58" s="82"/>
       <c r="F58" s="58"/>
       <c r="G58" s="39"/>
       <c r="H58" s="59"/>
@@ -2781,9 +2785,9 @@
     </row>
     <row r="59" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B59" s="78"/>
-      <c r="C59" s="98"/>
-      <c r="D59" s="99"/>
-      <c r="E59" s="100"/>
+      <c r="C59" s="80"/>
+      <c r="D59" s="81"/>
+      <c r="E59" s="82"/>
       <c r="F59" s="58"/>
       <c r="G59" s="39"/>
       <c r="H59" s="59"/>
@@ -2796,9 +2800,9 @@
     </row>
     <row r="60" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B60" s="78"/>
-      <c r="C60" s="98"/>
-      <c r="D60" s="99"/>
-      <c r="E60" s="100"/>
+      <c r="C60" s="80"/>
+      <c r="D60" s="81"/>
+      <c r="E60" s="82"/>
       <c r="F60" s="58"/>
       <c r="G60" s="39"/>
       <c r="H60" s="59"/>
@@ -2811,9 +2815,9 @@
     </row>
     <row r="61" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B61" s="78"/>
-      <c r="C61" s="98"/>
-      <c r="D61" s="99"/>
-      <c r="E61" s="100"/>
+      <c r="C61" s="80"/>
+      <c r="D61" s="81"/>
+      <c r="E61" s="82"/>
       <c r="F61" s="58"/>
       <c r="G61" s="39"/>
       <c r="H61" s="59"/>
@@ -2826,9 +2830,9 @@
     </row>
     <row r="62" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B62" s="78"/>
-      <c r="C62" s="98"/>
-      <c r="D62" s="99"/>
-      <c r="E62" s="100"/>
+      <c r="C62" s="80"/>
+      <c r="D62" s="81"/>
+      <c r="E62" s="82"/>
       <c r="F62" s="58"/>
       <c r="G62" s="39"/>
       <c r="H62" s="59"/>
@@ -2841,9 +2845,9 @@
     </row>
     <row r="63" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B63" s="78"/>
-      <c r="C63" s="98"/>
-      <c r="D63" s="99"/>
-      <c r="E63" s="100"/>
+      <c r="C63" s="80"/>
+      <c r="D63" s="81"/>
+      <c r="E63" s="82"/>
       <c r="F63" s="58"/>
       <c r="G63" s="39"/>
       <c r="H63" s="59"/>
@@ -2856,9 +2860,9 @@
     </row>
     <row r="64" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B64" s="78"/>
-      <c r="C64" s="98"/>
-      <c r="D64" s="99"/>
-      <c r="E64" s="100"/>
+      <c r="C64" s="80"/>
+      <c r="D64" s="81"/>
+      <c r="E64" s="82"/>
       <c r="F64" s="58"/>
       <c r="G64" s="39"/>
       <c r="H64" s="59"/>
@@ -2871,9 +2875,9 @@
     </row>
     <row r="65" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B65" s="78"/>
-      <c r="C65" s="98"/>
-      <c r="D65" s="99"/>
-      <c r="E65" s="100"/>
+      <c r="C65" s="80"/>
+      <c r="D65" s="81"/>
+      <c r="E65" s="82"/>
       <c r="F65" s="58"/>
       <c r="G65" s="39"/>
       <c r="H65" s="59"/>
@@ -2886,9 +2890,9 @@
     </row>
     <row r="66" spans="2:14" s="60" customFormat="1" ht="21" customHeight="1">
       <c r="B66" s="78"/>
-      <c r="C66" s="98"/>
-      <c r="D66" s="99"/>
-      <c r="E66" s="100"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="81"/>
+      <c r="E66" s="82"/>
       <c r="F66" s="58"/>
       <c r="G66" s="39"/>
       <c r="H66" s="59"/>
@@ -2901,11 +2905,11 @@
     </row>
     <row r="67" spans="2:14" s="60" customFormat="1" ht="18" customHeight="1">
       <c r="B67" s="63"/>
-      <c r="C67" s="88" t="s">
+      <c r="C67" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="D67" s="89"/>
-      <c r="E67" s="90"/>
+      <c r="D67" s="92"/>
+      <c r="E67" s="93"/>
       <c r="F67" s="58"/>
       <c r="G67" s="39"/>
       <c r="H67" s="59"/>
@@ -2922,11 +2926,11 @@
       <c r="D68" s="74"/>
       <c r="E68" s="74"/>
       <c r="F68" s="75"/>
-      <c r="G68" s="91" t="s">
+      <c r="G68" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="H68" s="92"/>
-      <c r="I68" s="93"/>
+      <c r="H68" s="95"/>
+      <c r="I68" s="96"/>
       <c r="J68" s="42">
         <f>SUM(J17:J66)</f>
         <v>0</v>
@@ -2942,11 +2946,11 @@
       <c r="D69" s="44"/>
       <c r="E69" s="44"/>
       <c r="F69" s="44"/>
-      <c r="G69" s="91" t="s">
+      <c r="G69" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="H69" s="92"/>
-      <c r="I69" s="93"/>
+      <c r="H69" s="95"/>
+      <c r="I69" s="96"/>
       <c r="J69" s="42">
         <f>J68</f>
         <v>0</v>
@@ -2957,10 +2961,10 @@
       <c r="N69" s="41"/>
     </row>
     <row r="70" spans="2:14" s="15" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="G70" s="94" t="s">
+      <c r="G70" s="97" t="s">
         <v>10</v>
       </c>
-      <c r="H70" s="95" t="s">
+      <c r="H70" s="98" t="s">
         <v>10</v>
       </c>
       <c r="I70" s="77"/>
@@ -2972,13 +2976,13 @@
     </row>
     <row r="71" spans="2:14" s="15" customFormat="1" ht="16.25" customHeight="1">
       <c r="E71" s="73"/>
-      <c r="G71" s="91" t="s">
+      <c r="G71" s="94" t="s">
         <v>15</v>
       </c>
-      <c r="H71" s="92" t="s">
+      <c r="H71" s="95" t="s">
         <v>16</v>
       </c>
-      <c r="I71" s="93"/>
+      <c r="I71" s="96"/>
       <c r="J71" s="64">
         <f>J69*0.05</f>
         <v>0</v>
@@ -2990,11 +2994,11 @@
     </row>
     <row r="72" spans="2:14" s="15" customFormat="1" ht="16">
       <c r="F72" s="19"/>
-      <c r="G72" s="91" t="s">
+      <c r="G72" s="94" t="s">
         <v>22</v>
       </c>
-      <c r="H72" s="92"/>
-      <c r="I72" s="93"/>
+      <c r="H72" s="95"/>
+      <c r="I72" s="96"/>
       <c r="J72" s="64">
         <f>J71+J69</f>
         <v>0</v>
@@ -3051,24 +3055,24 @@
       <c r="N76" s="11"/>
     </row>
     <row r="77" spans="2:14" ht="15.5" customHeight="1">
-      <c r="B77" s="96" t="s">
+      <c r="B77" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="C77" s="96"/>
+      <c r="C77" s="99"/>
       <c r="D77" s="18"/>
       <c r="E77" s="18"/>
       <c r="F77" s="19"/>
       <c r="G77" s="20"/>
-      <c r="H77" s="97" t="s">
+      <c r="H77" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="I77" s="97"/>
-      <c r="J77" s="97"/>
+      <c r="I77" s="100"/>
+      <c r="J77" s="100"/>
       <c r="K77" s="70"/>
     </row>
     <row r="78" spans="2:14">
-      <c r="B78" s="96"/>
-      <c r="C78" s="96"/>
+      <c r="B78" s="99"/>
+      <c r="C78" s="99"/>
       <c r="D78" s="8"/>
       <c r="E78" s="8"/>
       <c r="H78" s="21"/>
@@ -3093,12 +3097,12 @@
       <c r="C80" s="22"/>
       <c r="D80" s="22"/>
       <c r="E80" s="22"/>
-      <c r="H80" s="84"/>
-      <c r="I80" s="84"/>
-      <c r="J80" s="85"/>
+      <c r="H80" s="87"/>
+      <c r="I80" s="87"/>
+      <c r="J80" s="88"/>
       <c r="K80" s="71"/>
     </row>
-    <row r="81" spans="1:14" ht="16">
+    <row r="81" spans="2:14" ht="16">
       <c r="C81" s="23"/>
       <c r="D81" s="23"/>
       <c r="E81" s="23"/>
@@ -3107,7 +3111,7 @@
       <c r="J81" s="71"/>
       <c r="K81" s="71"/>
     </row>
-    <row r="82" spans="1:14">
+    <row r="82" spans="2:14">
       <c r="B82" s="24"/>
       <c r="F82" s="25"/>
       <c r="H82" s="26"/>
@@ -3115,7 +3119,7 @@
       <c r="J82" s="26"/>
       <c r="K82" s="26"/>
     </row>
-    <row r="83" spans="1:14">
+    <row r="83" spans="2:14">
       <c r="B83" s="28" t="s">
         <v>2</v>
       </c>
@@ -3123,7 +3127,7 @@
       <c r="M83" s="54"/>
       <c r="N83" s="34"/>
     </row>
-    <row r="84" spans="1:14" ht="18" customHeight="1">
+    <row r="84" spans="2:14" ht="18" customHeight="1">
       <c r="B84" s="35" t="s">
         <v>23</v>
       </c>
@@ -3131,7 +3135,7 @@
       <c r="M84" s="54"/>
       <c r="N84" s="34"/>
     </row>
-    <row r="85" spans="1:14" ht="18" customHeight="1">
+    <row r="85" spans="2:14" ht="18" customHeight="1">
       <c r="B85" s="101" t="s">
         <v>29</v>
       </c>
@@ -3145,18 +3149,23 @@
       <c r="M85" s="54"/>
       <c r="N85" s="34"/>
     </row>
-    <row r="86" spans="1:14" ht="18" customHeight="1">
-      <c r="B86" s="35" t="s">
+    <row r="86" spans="2:14" ht="18" customHeight="1">
+      <c r="B86" s="102" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="36"/>
-      <c r="D86" s="36"/>
-      <c r="E86" s="36"/>
+      <c r="C86" s="102"/>
+      <c r="D86" s="102"/>
+      <c r="E86" s="102"/>
+      <c r="F86" s="102"/>
+      <c r="G86" s="102"/>
+      <c r="H86" s="102"/>
+      <c r="I86" s="102"/>
+      <c r="J86" s="102"/>
       <c r="L86" s="54"/>
       <c r="M86" s="54"/>
       <c r="N86" s="34"/>
     </row>
-    <row r="87" spans="1:14" s="37" customFormat="1" ht="18" customHeight="1">
+    <row r="87" spans="2:14" s="37" customFormat="1" ht="18" customHeight="1">
       <c r="B87" s="35" t="s">
         <v>39</v>
       </c>
@@ -3168,7 +3177,7 @@
       <c r="L87" s="55"/>
       <c r="M87" s="55"/>
     </row>
-    <row r="88" spans="1:14" ht="17">
+    <row r="88" spans="2:14" ht="17">
       <c r="B88" s="35" t="s">
         <v>27</v>
       </c>
@@ -3185,7 +3194,7 @@
       <c r="M88" s="54"/>
       <c r="N88" s="34"/>
     </row>
-    <row r="89" spans="1:14">
+    <row r="89" spans="2:14">
       <c r="B89" s="35" t="s">
         <v>28</v>
       </c>
@@ -3198,136 +3207,218 @@
       <c r="M89" s="54"/>
       <c r="N89" s="34"/>
     </row>
-    <row r="90" spans="1:14" ht="16.5">
-      <c r="B90" s="35"/>
-      <c r="C90" s="79"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
+    <row r="90" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B90" s="102"/>
+      <c r="C90" s="102"/>
+      <c r="D90" s="102"/>
+      <c r="E90" s="102"/>
+      <c r="F90" s="102"/>
+      <c r="G90" s="102"/>
+      <c r="H90" s="102"/>
+      <c r="I90" s="102"/>
+      <c r="J90" s="102"/>
       <c r="K90" s="1"/>
       <c r="L90" s="54"/>
       <c r="M90" s="54"/>
       <c r="N90" s="34"/>
     </row>
-    <row r="91" spans="1:14" s="28" customFormat="1">
-      <c r="A91" s="27"/>
-      <c r="B91" s="28" t="s">
+    <row r="91" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B91" s="102"/>
+      <c r="C91" s="102"/>
+      <c r="D91" s="102"/>
+      <c r="E91" s="102"/>
+      <c r="F91" s="102"/>
+      <c r="G91" s="102"/>
+      <c r="H91" s="102"/>
+      <c r="I91" s="102"/>
+      <c r="J91" s="102"/>
+      <c r="K91" s="1"/>
+      <c r="L91" s="54"/>
+      <c r="M91" s="54"/>
+      <c r="N91" s="34"/>
+    </row>
+    <row r="92" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B92" s="102"/>
+      <c r="C92" s="102"/>
+      <c r="D92" s="102"/>
+      <c r="E92" s="102"/>
+      <c r="F92" s="102"/>
+      <c r="G92" s="102"/>
+      <c r="H92" s="102"/>
+      <c r="I92" s="102"/>
+      <c r="J92" s="102"/>
+      <c r="K92" s="1"/>
+      <c r="L92" s="54"/>
+      <c r="M92" s="54"/>
+      <c r="N92" s="34"/>
+    </row>
+    <row r="93" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B93" s="102"/>
+      <c r="C93" s="102"/>
+      <c r="D93" s="102"/>
+      <c r="E93" s="102"/>
+      <c r="F93" s="102"/>
+      <c r="G93" s="102"/>
+      <c r="H93" s="102"/>
+      <c r="I93" s="102"/>
+      <c r="J93" s="102"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="54"/>
+      <c r="M93" s="54"/>
+      <c r="N93" s="34"/>
+    </row>
+    <row r="94" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B94" s="102"/>
+      <c r="C94" s="102"/>
+      <c r="D94" s="102"/>
+      <c r="E94" s="102"/>
+      <c r="F94" s="102"/>
+      <c r="G94" s="102"/>
+      <c r="H94" s="102"/>
+      <c r="I94" s="102"/>
+      <c r="J94" s="102"/>
+      <c r="K94" s="1"/>
+      <c r="L94" s="54"/>
+      <c r="M94" s="54"/>
+      <c r="N94" s="34"/>
+    </row>
+    <row r="95" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B95" s="102"/>
+      <c r="C95" s="102"/>
+      <c r="D95" s="102"/>
+      <c r="E95" s="102"/>
+      <c r="F95" s="102"/>
+      <c r="G95" s="102"/>
+      <c r="H95" s="102"/>
+      <c r="I95" s="102"/>
+      <c r="J95" s="102"/>
+      <c r="K95" s="1"/>
+      <c r="L95" s="54"/>
+      <c r="M95" s="54"/>
+      <c r="N95" s="34"/>
+    </row>
+    <row r="96" spans="2:14" ht="18" hidden="1" customHeight="1">
+      <c r="B96" s="102"/>
+      <c r="C96" s="102"/>
+      <c r="D96" s="102"/>
+      <c r="E96" s="102"/>
+      <c r="F96" s="102"/>
+      <c r="G96" s="102"/>
+      <c r="H96" s="102"/>
+      <c r="I96" s="102"/>
+      <c r="J96" s="102"/>
+      <c r="K96" s="1"/>
+      <c r="L96" s="54"/>
+      <c r="M96" s="54"/>
+      <c r="N96" s="34"/>
+    </row>
+    <row r="97" spans="1:14" ht="18" hidden="1" customHeight="1">
+      <c r="B97" s="102"/>
+      <c r="C97" s="102"/>
+      <c r="D97" s="102"/>
+      <c r="E97" s="102"/>
+      <c r="F97" s="102"/>
+      <c r="G97" s="102"/>
+      <c r="H97" s="102"/>
+      <c r="I97" s="102"/>
+      <c r="J97" s="102"/>
+      <c r="K97" s="1"/>
+      <c r="L97" s="54"/>
+      <c r="M97" s="54"/>
+      <c r="N97" s="34"/>
+    </row>
+    <row r="98" spans="1:14" ht="16.5">
+      <c r="B98" s="35"/>
+      <c r="C98" s="79"/>
+      <c r="G98" s="1"/>
+      <c r="H98" s="1"/>
+      <c r="I98" s="1"/>
+      <c r="J98" s="1"/>
+      <c r="K98" s="1"/>
+      <c r="L98" s="54"/>
+      <c r="M98" s="54"/>
+      <c r="N98" s="34"/>
+    </row>
+    <row r="99" spans="1:14" s="28" customFormat="1">
+      <c r="A99" s="27"/>
+      <c r="B99" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="29"/>
-      <c r="F91" s="27"/>
-      <c r="G91" s="29" t="s">
+      <c r="C99" s="29"/>
+      <c r="D99" s="29"/>
+      <c r="E99" s="29"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="H91" s="27"/>
-      <c r="I91" s="27"/>
-      <c r="J91" s="27"/>
-      <c r="K91" s="27"/>
-      <c r="L91" s="56"/>
-      <c r="M91" s="56"/>
-      <c r="N91" s="30"/>
-    </row>
-    <row r="92" spans="1:14" s="28" customFormat="1" ht="23">
-      <c r="G92" s="86" t="s">
+      <c r="H99" s="27"/>
+      <c r="I99" s="27"/>
+      <c r="J99" s="27"/>
+      <c r="K99" s="27"/>
+      <c r="L99" s="56"/>
+      <c r="M99" s="56"/>
+      <c r="N99" s="30"/>
+    </row>
+    <row r="100" spans="1:14" s="28" customFormat="1" ht="23">
+      <c r="G100" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="H92" s="86"/>
-      <c r="I92" s="86"/>
-      <c r="J92" s="86"/>
-      <c r="K92" s="31"/>
-      <c r="L92" s="49"/>
-      <c r="M92" s="49"/>
-      <c r="N92" s="6"/>
-    </row>
-    <row r="93" spans="1:14" s="28" customFormat="1" ht="23">
-      <c r="G93" s="86"/>
-      <c r="H93" s="86"/>
-      <c r="I93" s="86"/>
-      <c r="J93" s="86"/>
-      <c r="K93" s="31"/>
-      <c r="L93" s="49"/>
-      <c r="M93" s="49"/>
-      <c r="N93" s="6"/>
-    </row>
-    <row r="94" spans="1:14" s="28" customFormat="1" ht="23.5" thickBot="1">
-      <c r="B94" s="32"/>
-      <c r="C94" s="32"/>
-      <c r="G94" s="87"/>
-      <c r="H94" s="87"/>
-      <c r="I94" s="87"/>
-      <c r="J94" s="87"/>
-      <c r="K94" s="31"/>
-      <c r="L94" s="49"/>
-      <c r="M94" s="49"/>
-      <c r="N94" s="6"/>
-    </row>
-    <row r="95" spans="1:14" s="33" customFormat="1" ht="18" customHeight="1">
-      <c r="B95" s="33" t="s">
+      <c r="H100" s="89"/>
+      <c r="I100" s="89"/>
+      <c r="J100" s="89"/>
+      <c r="K100" s="31"/>
+      <c r="L100" s="49"/>
+      <c r="M100" s="49"/>
+      <c r="N100" s="6"/>
+    </row>
+    <row r="101" spans="1:14" s="28" customFormat="1" ht="23">
+      <c r="G101" s="89"/>
+      <c r="H101" s="89"/>
+      <c r="I101" s="89"/>
+      <c r="J101" s="89"/>
+      <c r="K101" s="31"/>
+      <c r="L101" s="49"/>
+      <c r="M101" s="49"/>
+      <c r="N101" s="6"/>
+    </row>
+    <row r="102" spans="1:14" s="28" customFormat="1" ht="23.5" thickBot="1">
+      <c r="B102" s="32"/>
+      <c r="C102" s="32"/>
+      <c r="G102" s="90"/>
+      <c r="H102" s="90"/>
+      <c r="I102" s="90"/>
+      <c r="J102" s="90"/>
+      <c r="K102" s="31"/>
+      <c r="L102" s="49"/>
+      <c r="M102" s="49"/>
+      <c r="N102" s="6"/>
+    </row>
+    <row r="103" spans="1:14" s="33" customFormat="1" ht="18" customHeight="1">
+      <c r="B103" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="G95" s="33" t="s">
+      <c r="G103" s="33" t="s">
         <v>6</v>
       </c>
-      <c r="L95" s="53"/>
-      <c r="M95" s="53"/>
-      <c r="N95" s="11"/>
+      <c r="L103" s="53"/>
+      <c r="M103" s="53"/>
+      <c r="N103" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="63">
-    <mergeCell ref="C65:E65"/>
-    <mergeCell ref="C66:E66"/>
-    <mergeCell ref="C60:E60"/>
-    <mergeCell ref="C61:E61"/>
-    <mergeCell ref="C62:E62"/>
-    <mergeCell ref="C63:E63"/>
-    <mergeCell ref="C64:E64"/>
-    <mergeCell ref="C55:E55"/>
-    <mergeCell ref="C56:E56"/>
-    <mergeCell ref="C57:E57"/>
-    <mergeCell ref="C58:E58"/>
-    <mergeCell ref="C59:E59"/>
-    <mergeCell ref="C50:E50"/>
-    <mergeCell ref="C51:E51"/>
-    <mergeCell ref="C52:E52"/>
-    <mergeCell ref="C53:E53"/>
-    <mergeCell ref="C54:E54"/>
-    <mergeCell ref="C45:E45"/>
-    <mergeCell ref="C46:E46"/>
-    <mergeCell ref="C47:E47"/>
-    <mergeCell ref="C48:E48"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="C40:E40"/>
-    <mergeCell ref="C41:E41"/>
-    <mergeCell ref="C42:E42"/>
-    <mergeCell ref="C43:E43"/>
-    <mergeCell ref="C44:E44"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="C36:E36"/>
-    <mergeCell ref="C37:E37"/>
-    <mergeCell ref="C38:E38"/>
-    <mergeCell ref="C39:E39"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="C32:E32"/>
-    <mergeCell ref="C33:E33"/>
-    <mergeCell ref="C34:E34"/>
-    <mergeCell ref="C25:E25"/>
-    <mergeCell ref="C26:E26"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C28:E28"/>
-    <mergeCell ref="C29:E29"/>
-    <mergeCell ref="C20:E20"/>
-    <mergeCell ref="C21:E21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="C23:E23"/>
-    <mergeCell ref="C24:E24"/>
+  <mergeCells count="72">
+    <mergeCell ref="B94:J94"/>
+    <mergeCell ref="B95:J95"/>
+    <mergeCell ref="B96:J96"/>
+    <mergeCell ref="B97:J97"/>
+    <mergeCell ref="B86:J86"/>
+    <mergeCell ref="B90:J90"/>
+    <mergeCell ref="B91:J91"/>
+    <mergeCell ref="B92:J92"/>
+    <mergeCell ref="B93:J93"/>
     <mergeCell ref="B15:C15"/>
     <mergeCell ref="C16:E16"/>
     <mergeCell ref="H80:J80"/>
-    <mergeCell ref="G92:J94"/>
+    <mergeCell ref="G100:J102"/>
     <mergeCell ref="C67:E67"/>
     <mergeCell ref="G69:I69"/>
     <mergeCell ref="G70:H70"/>
@@ -3340,11 +3431,58 @@
     <mergeCell ref="G68:I68"/>
     <mergeCell ref="C18:E18"/>
     <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:E20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="C22:E22"/>
+    <mergeCell ref="C23:E23"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="C26:E26"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C28:E28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="C30:E30"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="C32:E32"/>
+    <mergeCell ref="C33:E33"/>
+    <mergeCell ref="C34:E34"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="C37:E37"/>
+    <mergeCell ref="C38:E38"/>
+    <mergeCell ref="C39:E39"/>
+    <mergeCell ref="C40:E40"/>
+    <mergeCell ref="C41:E41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="C44:E44"/>
+    <mergeCell ref="C45:E45"/>
+    <mergeCell ref="C46:E46"/>
+    <mergeCell ref="C47:E47"/>
+    <mergeCell ref="C48:E48"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="C50:E50"/>
+    <mergeCell ref="C51:E51"/>
+    <mergeCell ref="C52:E52"/>
+    <mergeCell ref="C53:E53"/>
+    <mergeCell ref="C54:E54"/>
+    <mergeCell ref="C55:E55"/>
+    <mergeCell ref="C56:E56"/>
+    <mergeCell ref="C57:E57"/>
+    <mergeCell ref="C58:E58"/>
+    <mergeCell ref="C59:E59"/>
+    <mergeCell ref="C65:E65"/>
+    <mergeCell ref="C66:E66"/>
+    <mergeCell ref="C60:E60"/>
+    <mergeCell ref="C61:E61"/>
+    <mergeCell ref="C62:E62"/>
+    <mergeCell ref="C63:E63"/>
+    <mergeCell ref="C64:E64"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="41" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="68" fitToHeight="0" orientation="portrait"/>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/templates/quotation_template.xlsx
+++ b/templates/quotation_template.xlsx
@@ -467,7 +467,7 @@
       <charset val="136"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -495,6 +495,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -644,7 +650,7 @@
     </xf>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="103">
+  <cellXfs count="104">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="11" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
@@ -919,6 +925,9 @@
     </xf>
     <xf numFmtId="37" fontId="31" fillId="0" borderId="0" xfId="14" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="6" xfId="13" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="28">
